--- a/research/traditional_assets/database/data/mauritius/mauritius_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.062</v>
+        <v>0.11085</v>
       </c>
       <c r="E2">
-        <v>-0.08599999999999999</v>
+        <v>0.08910000000000001</v>
+      </c>
+      <c r="F2">
+        <v>0.175</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>236.25</v>
+        <v>299.1</v>
       </c>
       <c r="L2">
-        <v>0.3699498903852176</v>
+        <v>0.4169222191246167</v>
       </c>
       <c r="M2">
-        <v>40.4</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="N2">
-        <v>0.02004067662086413</v>
+        <v>0.04237860296027006</v>
       </c>
       <c r="O2">
-        <v>0.171005291005291</v>
+        <v>0.2728184553660983</v>
       </c>
       <c r="P2">
-        <v>40.4</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="Q2">
-        <v>0.02004067662086413</v>
+        <v>0.04237860296027006</v>
       </c>
       <c r="R2">
-        <v>0.171005291005291</v>
+        <v>0.2728184553660983</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2594.9</v>
+        <v>1801.8</v>
       </c>
       <c r="V2">
-        <v>1.287216627808919</v>
+        <v>0.9357569462477279</v>
       </c>
       <c r="W2">
-        <v>0.05708937763219467</v>
+        <v>0.1283602444354297</v>
       </c>
       <c r="X2">
-        <v>0.080876035941535</v>
+        <v>0.1469589948835194</v>
       </c>
       <c r="Y2">
-        <v>-0.02378665830934033</v>
+        <v>-0.0185987504480897</v>
       </c>
       <c r="Z2">
-        <v>0.2271708583828394</v>
+        <v>0.3316689782709201</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05697080037070942</v>
+        <v>0.09313368203582181</v>
       </c>
       <c r="AC2">
-        <v>-0.05697080037070942</v>
+        <v>-0.09313368203582181</v>
       </c>
       <c r="AD2">
-        <v>2381</v>
+        <v>2937.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2381</v>
+        <v>2937.3</v>
       </c>
       <c r="AG2">
-        <v>-213.9000000000001</v>
+        <v>1135.5</v>
       </c>
       <c r="AH2">
-        <v>0.5415178876026292</v>
+        <v>0.6040347125113104</v>
       </c>
       <c r="AI2">
-        <v>0.4975758588982697</v>
+        <v>0.5524251941848</v>
       </c>
       <c r="AJ2">
-        <v>-0.1187014428412875</v>
+        <v>0.3709572035282588</v>
       </c>
       <c r="AK2">
-        <v>-0.09765785508834411</v>
+        <v>0.323016527750121</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.062</v>
+        <v>0.07769999999999999</v>
       </c>
       <c r="E3">
-        <v>0.0493</v>
+        <v>0.08740000000000001</v>
+      </c>
+      <c r="F3">
+        <v>0.175</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>197.5</v>
+        <v>225.6</v>
       </c>
       <c r="L3">
-        <v>0.4647058823529412</v>
+        <v>0.4849527085124677</v>
       </c>
       <c r="M3">
-        <v>40.4</v>
+        <v>70.3</v>
       </c>
       <c r="N3">
-        <v>0.02329201498991064</v>
+        <v>0.04221461598510779</v>
       </c>
       <c r="O3">
-        <v>0.2045569620253165</v>
+        <v>0.311613475177305</v>
       </c>
       <c r="P3">
-        <v>40.4</v>
+        <v>70.3</v>
       </c>
       <c r="Q3">
-        <v>0.02329201498991064</v>
+        <v>0.04221461598510779</v>
       </c>
       <c r="R3">
-        <v>0.2045569620253165</v>
+        <v>0.311613475177305</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1540.7</v>
+        <v>1436.5</v>
       </c>
       <c r="V3">
-        <v>0.8882675122513694</v>
+        <v>0.8626073380171742</v>
       </c>
       <c r="W3">
-        <v>0.1217332347140039</v>
+        <v>0.1331287619497226</v>
       </c>
       <c r="X3">
-        <v>0.080876035941535</v>
+        <v>0.1341774064964991</v>
       </c>
       <c r="Y3">
-        <v>0.04085719877246893</v>
+        <v>-0.001048644546776417</v>
       </c>
       <c r="Z3">
-        <v>0.2266666666666667</v>
+        <v>0.2356397528112654</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0566732915040421</v>
+        <v>0.09231585100464329</v>
       </c>
       <c r="AC3">
-        <v>-0.0566732915040421</v>
+        <v>-0.09231585100464329</v>
       </c>
       <c r="AD3">
-        <v>1820.3</v>
+        <v>2383.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1820.3</v>
+        <v>2383.1</v>
       </c>
       <c r="AG3">
-        <v>279.5999999999999</v>
+        <v>946.5999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.5120681894902667</v>
+        <v>0.5886523070842803</v>
       </c>
       <c r="AI3">
-        <v>0.5079812468605236</v>
+        <v>0.5710349124194283</v>
       </c>
       <c r="AJ3">
-        <v>0.1388213097661486</v>
+        <v>0.3624181630230867</v>
       </c>
       <c r="AK3">
-        <v>0.1368776619180496</v>
+        <v>0.345878398129202</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ABC Banking Corporation Ltd (MUSE:ABCB.I0000)</t>
+          <t>SBM Holdings Ltd (MUSE:SBMH.N0000)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,10 +838,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0297</v>
+        <v>0.144</v>
       </c>
       <c r="E4">
-        <v>-0.121</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,206 +856,90 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>2.15</v>
+        <v>73.5</v>
       </c>
       <c r="L4">
-        <v>0.2047619047619048</v>
+        <v>0.2914353687549564</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>11.3</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.0434281322059954</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.1537414965986395</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>11.3</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.0434281322059954</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.1537414965986395</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>104.1</v>
+        <v>365.3</v>
       </c>
       <c r="V4">
-        <v>3.528813559322034</v>
+        <v>1.403920061491161</v>
       </c>
       <c r="W4">
-        <v>0.04545454545454546</v>
+        <v>0.1235917269211367</v>
       </c>
       <c r="X4">
-        <v>0.0663923514252803</v>
+        <v>0.1597405832705397</v>
       </c>
       <c r="Y4">
-        <v>-0.02093780597073484</v>
+        <v>-0.03614885634940303</v>
       </c>
       <c r="Z4">
-        <v>0.9545454545454546</v>
+        <v>1.335805084745762</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05697080037070942</v>
+        <v>0.09395151306700035</v>
       </c>
       <c r="AC4">
-        <v>-0.05697080037070942</v>
+        <v>-0.09395151306700035</v>
       </c>
       <c r="AD4">
-        <v>16.5</v>
+        <v>554.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>16.5</v>
+        <v>554.2</v>
       </c>
       <c r="AG4">
-        <v>-87.59999999999999</v>
+        <v>188.9</v>
       </c>
       <c r="AH4">
-        <v>0.358695652173913</v>
+        <v>0.6805009823182711</v>
       </c>
       <c r="AI4">
-        <v>0.2623211446740858</v>
+        <v>0.4845252666550096</v>
       </c>
       <c r="AJ4">
-        <v>1.507745266781412</v>
+        <v>0.4206190158093966</v>
       </c>
       <c r="AK4">
-        <v>2.12621359223301</v>
+        <v>0.242646114322415</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Mauritius</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SBM Holdings Ltd (MUSE:SBMH.N0000)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.09140000000000001</v>
-      </c>
-      <c r="E5">
-        <v>-0.08599999999999999</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>36.6</v>
-      </c>
-      <c r="L5">
-        <v>0.1802067946824225</v>
-      </c>
-      <c r="M5">
-        <v>-0</v>
-      </c>
-      <c r="N5">
-        <v>-0</v>
-      </c>
-      <c r="O5">
-        <v>-0</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>-0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>950.1</v>
-      </c>
-      <c r="V5">
-        <v>3.771734815402938</v>
-      </c>
-      <c r="W5">
-        <v>0.05708937763219467</v>
-      </c>
-      <c r="X5">
-        <v>0.1137033512585855</v>
-      </c>
-      <c r="Y5">
-        <v>-0.05661397362639085</v>
-      </c>
-      <c r="Z5">
-        <v>0.2195438330991244</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.05895386060588878</v>
-      </c>
-      <c r="AC5">
-        <v>-0.05895386060588878</v>
-      </c>
-      <c r="AD5">
-        <v>544.2</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>544.2</v>
-      </c>
-      <c r="AG5">
-        <v>-405.9</v>
-      </c>
-      <c r="AH5">
-        <v>0.6835824645145082</v>
-      </c>
-      <c r="AI5">
-        <v>0.4778294845903943</v>
-      </c>
-      <c r="AJ5">
-        <v>2.635714285714286</v>
-      </c>
-      <c r="AK5">
-        <v>-2.149894067796609</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/mauritius/mauritius_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.11085</v>
+        <v>0.1405</v>
       </c>
       <c r="E2">
-        <v>0.08910000000000001</v>
+        <v>0.1615</v>
       </c>
       <c r="F2">
-        <v>0.175</v>
+        <v>0.187</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +609,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>299.1</v>
+        <v>444.9</v>
       </c>
       <c r="L2">
-        <v>0.4169222191246167</v>
+        <v>0.4452562049639712</v>
       </c>
       <c r="M2">
-        <v>81.59999999999999</v>
+        <v>82.39999999999999</v>
       </c>
       <c r="N2">
-        <v>0.04237860296027006</v>
+        <v>0.03959254276379012</v>
       </c>
       <c r="O2">
-        <v>0.2728184553660983</v>
+        <v>0.1852101595864239</v>
       </c>
       <c r="P2">
-        <v>81.59999999999999</v>
+        <v>82.39999999999999</v>
       </c>
       <c r="Q2">
-        <v>0.04237860296027006</v>
+        <v>0.03959254276379012</v>
       </c>
       <c r="R2">
-        <v>0.2728184553660983</v>
+        <v>0.1852101595864239</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1801.8</v>
+        <v>2044.9</v>
       </c>
       <c r="V2">
-        <v>0.9357569462477279</v>
+        <v>0.9825581395348838</v>
       </c>
       <c r="W2">
-        <v>0.1283602444354297</v>
+        <v>0.192779173809601</v>
       </c>
       <c r="X2">
-        <v>0.1469589948835194</v>
+        <v>0.1123943702479083</v>
       </c>
       <c r="Y2">
-        <v>-0.0185987504480897</v>
+        <v>0.08038480356169271</v>
       </c>
       <c r="Z2">
-        <v>0.3316689782709201</v>
+        <v>0.3138092396595584</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.09313368203582181</v>
+        <v>0.07892797199616366</v>
       </c>
       <c r="AC2">
-        <v>-0.09313368203582181</v>
+        <v>-0.07892797199616366</v>
       </c>
       <c r="AD2">
-        <v>2937.3</v>
+        <v>2912.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2937.3</v>
+        <v>2912.9</v>
       </c>
       <c r="AG2">
-        <v>1135.5</v>
+        <v>868</v>
       </c>
       <c r="AH2">
-        <v>0.6040347125113104</v>
+        <v>0.5832682565427204</v>
       </c>
       <c r="AI2">
-        <v>0.5524251941848</v>
+        <v>0.5068557508265182</v>
       </c>
       <c r="AJ2">
-        <v>0.3709572035282588</v>
+        <v>0.294317102943171</v>
       </c>
       <c r="AK2">
-        <v>0.323016527750121</v>
+        <v>0.2344615218389563</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.07769999999999999</v>
+        <v>0.129</v>
       </c>
       <c r="E3">
-        <v>0.08740000000000001</v>
+        <v>0.143</v>
       </c>
       <c r="F3">
-        <v>0.175</v>
+        <v>0.187</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +734,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>225.6</v>
+        <v>335.7</v>
       </c>
       <c r="L3">
-        <v>0.4849527085124677</v>
+        <v>0.5004472271914132</v>
       </c>
       <c r="M3">
-        <v>70.3</v>
+        <v>70.8</v>
       </c>
       <c r="N3">
-        <v>0.04221461598510779</v>
+        <v>0.039023314777049</v>
       </c>
       <c r="O3">
-        <v>0.311613475177305</v>
+        <v>0.2109025915996425</v>
       </c>
       <c r="P3">
-        <v>70.3</v>
+        <v>70.8</v>
       </c>
       <c r="Q3">
-        <v>0.04221461598510779</v>
+        <v>0.039023314777049</v>
       </c>
       <c r="R3">
-        <v>0.311613475177305</v>
+        <v>0.2109025915996425</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +764,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1436.5</v>
+        <v>1787</v>
       </c>
       <c r="V3">
-        <v>0.8626073380171742</v>
+        <v>0.9849528743868159</v>
       </c>
       <c r="W3">
-        <v>0.1331287619497226</v>
+        <v>0.1950156849076333</v>
       </c>
       <c r="X3">
-        <v>0.1341774064964991</v>
+        <v>0.1040033696461202</v>
       </c>
       <c r="Y3">
-        <v>-0.001048644546776417</v>
+        <v>0.09101231526151306</v>
       </c>
       <c r="Z3">
-        <v>0.2356397528112654</v>
+        <v>0.251424287856072</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.09231585100464329</v>
+        <v>0.07821542776214176</v>
       </c>
       <c r="AC3">
-        <v>-0.09231585100464329</v>
+        <v>-0.07821542776214176</v>
       </c>
       <c r="AD3">
-        <v>2383.1</v>
+        <v>2390</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2383.1</v>
+        <v>2390</v>
       </c>
       <c r="AG3">
-        <v>946.5999999999999</v>
+        <v>603</v>
       </c>
       <c r="AH3">
-        <v>0.5886523070842803</v>
+        <v>0.5684656185334063</v>
       </c>
       <c r="AI3">
-        <v>0.5710349124194283</v>
+        <v>0.5297572869333924</v>
       </c>
       <c r="AJ3">
-        <v>0.3624181630230867</v>
+        <v>0.2494518677863732</v>
       </c>
       <c r="AK3">
-        <v>0.345878398129202</v>
+        <v>0.2213250137639934</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.144</v>
+        <v>0.152</v>
       </c>
       <c r="E4">
-        <v>0.09080000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,28 +856,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>73.5</v>
+        <v>109.2</v>
       </c>
       <c r="L4">
-        <v>0.2914353687549564</v>
+        <v>0.3325213154689404</v>
       </c>
       <c r="M4">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="N4">
-        <v>0.0434281322059954</v>
+        <v>0.04346197077557138</v>
       </c>
       <c r="O4">
-        <v>0.1537414965986395</v>
+        <v>0.1062271062271062</v>
       </c>
       <c r="P4">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="Q4">
-        <v>0.0434281322059954</v>
+        <v>0.04346197077557138</v>
       </c>
       <c r="R4">
-        <v>0.1537414965986395</v>
+        <v>0.1062271062271062</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -886,55 +886,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>365.3</v>
+        <v>257.9</v>
       </c>
       <c r="V4">
-        <v>1.403920061491161</v>
+        <v>0.9662795054327463</v>
       </c>
       <c r="W4">
-        <v>0.1235917269211367</v>
+        <v>0.1905426627115687</v>
       </c>
       <c r="X4">
-        <v>0.1597405832705397</v>
+        <v>0.1207853708496963</v>
       </c>
       <c r="Y4">
-        <v>-0.03614885634940303</v>
+        <v>0.06975729186187239</v>
       </c>
       <c r="Z4">
-        <v>1.335805084745762</v>
+        <v>0.636310792482077</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.09395151306700035</v>
+        <v>0.07964051623018559</v>
       </c>
       <c r="AC4">
-        <v>-0.09395151306700035</v>
+        <v>-0.07964051623018559</v>
       </c>
       <c r="AD4">
-        <v>554.2</v>
+        <v>522.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>554.2</v>
+        <v>522.9</v>
       </c>
       <c r="AG4">
-        <v>188.9</v>
+        <v>265</v>
       </c>
       <c r="AH4">
-        <v>0.6805009823182711</v>
+        <v>0.6620663459103571</v>
       </c>
       <c r="AI4">
-        <v>0.4845252666550096</v>
+        <v>0.4232294617563739</v>
       </c>
       <c r="AJ4">
-        <v>0.4206190158093966</v>
+        <v>0.4982139499905998</v>
       </c>
       <c r="AK4">
-        <v>0.242646114322415</v>
+        <v>0.2710720130932897</v>
       </c>
       <c r="AL4">
         <v>0</v>
